--- a/dist/Datas/Export Inscription FaceToFace pour admin Formateur1752411459.xlsx
+++ b/dist/Datas/Export Inscription FaceToFace pour admin Formateur1752411459.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmhe-my.sharepoint.com/personal/christophe_desandiego_fr_toyota-industries_eu/Documents/Dokument/00-Documents_AE/Documents A_E/00-Dev/Generator/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_27B79DAFA2D8E162012D8E4FBC0EA568A06280CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24908EE1-8317-4054-8AEC-377CE82D7B5B}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_27B79DAFA2D8E162012D8E4FBC0EA568A06280CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07AF6011-47EC-4AA9-BA9E-A27490ABFA65}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Inscription FaceToFace p" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Export Inscription FaceToFace p'!$A$1:$Q$671</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5705,11 +5718,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -5732,9 +5751,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -25462,7 +25482,7 @@
       <c r="F367" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="G367" s="1" t="s">
+      <c r="G367" s="2" t="s">
         <v>1090</v>
       </c>
       <c r="H367" s="1" t="s">
@@ -41610,6 +41630,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:Q671" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Information classification: Internal</oddFooter>

--- a/dist/Datas/Export Inscription FaceToFace pour admin Formateur1752411459.xlsx
+++ b/dist/Datas/Export Inscription FaceToFace pour admin Formateur1752411459.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmhe-my.sharepoint.com/personal/christophe_desandiego_fr_toyota-industries_eu/Documents/Dokument/00-Documents_AE/Documents A_E/00-Dev/Generator/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="11_27B79DAFA2D8E162012D8E4FBC0EA568A06280CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07AF6011-47EC-4AA9-BA9E-A27490ABFA65}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_27B79DAFA2D8E162012D8E4FBC0EA568A06280CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44AE8755-F9EC-40DB-95FD-FD6181926E23}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Inscription FaceToFace p" sheetId="1" r:id="rId1"/>
@@ -41630,7 +41630,6 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:Q671" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;R_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Information classification: Internal</oddFooter>

--- a/dist/Datas/Export Inscription FaceToFace pour admin Formateur1752411459.xlsx
+++ b/dist/Datas/Export Inscription FaceToFace pour admin Formateur1752411459.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tmhe-my.sharepoint.com/personal/christophe_desandiego_fr_toyota-industries_eu/Documents/Dokument/00-Documents_AE/Documents A_E/00-Dev/Generator/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_27B79DAFA2D8E162012D8E4FBC0EA568A06280CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44AE8755-F9EC-40DB-95FD-FD6181926E23}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_27B79DAFA2D8E162012D8E4FBC0EA568A06280CE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7C30ACC-DC59-418E-A2CD-0DF5711B18E4}"/>
   <bookViews>
     <workbookView xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
